--- a/TAVRIDA_B1510261835045.xlsx
+++ b/TAVRIDA_B1510261835045.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Себестоимость" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маржа" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены для заявки" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поставщики (КП)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1409,4 +1410,251 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Кому отправить запрос КП по «Таврида.Арт» — нужна цена и наличие на 145 комплектов (р. 50–54, обувь 42–45), поставка в Судак за 10 дней</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Поставщик</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Какие позиции запросить</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Телефон</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Сайт</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Урсус</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>производитель, Долгопрудный</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>1 костюм (+наколенники/налокотники Блок-Х), 2 флисовая кофта, 3 зимняя куртка «Охрана», 4 шапка, 7 перчатки, 8 снуд</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>8 (495) 564-88-88</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>zakaz@ursu.ru</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ursus.ru</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>костюм, куртка, снуд — в наличии по оптовым ценам; основной поставщик</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Сплав</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>производитель, Москва</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>1 костюм, 2 флисовая кофта (Кречет Pro), 3 зимняя куртка, 5 полуботинки 10717, 6 жилет разгрузочный</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+7 495 984-28-83 (опт)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>opt@splav.ru</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.splav.ru</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>оптовый отдел; цены на сайте — розница, просить опт</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Garsing</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>производитель обуви и снаряжения</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>5 полуботинки утеплённые («Путешественник флис»), 7 перчатки зимние тактические (ТУЧИ)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>+7 (498) 602-69-01</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>marketing@garsing.ru</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>https://garsing.ru</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>уточнить чёрный цвет и наличие размеров 42–45</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ГК «Спецобъединение»</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>производитель СИЗ, Москва</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>3 зимняя куртка, 5 полуботинки утеплённые, 7 перчатки — запасной вариант</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+7 (495) 011-44-00</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>mail@spets.ru</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.spets.ru</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>прайс 2026 на сайте (price_msk.xls)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/TAVRIDA_B1510261835045.xlsx
+++ b/TAVRIDA_B1510261835045.xlsx
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>производитель, Долгопрудный</t>
+          <t>производитель — подтверждено на сайте: «собственное производство одежды и обуви с 1998 г.»</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>производитель, Москва</t>
+          <t>производитель — подтверждено: 3 фабрики (Москва, Тверь, Новозыбков)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>производитель обуви и снаряжения</t>
+          <t>бренд обуви/снаряжения — собственное производство НЕ подтверждено</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>производитель СИЗ, Москва</t>
+          <t>оптовик/поставщик СИЗ — производство НЕ подтверждено</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">

--- a/TAVRIDA_B1510261835045.xlsx
+++ b/TAVRIDA_B1510261835045.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Себестоимость" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маржа" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены для заявки" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поставщики (КП)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Себестоимость" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маржа" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены для заявки" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поставщики (КП)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="#,##0&quot; ₽&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,24 +87,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -111,14 +125,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -491,6 +499,240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>АНО «Таврида.Арт» — форменная одежда службы безопасности. Всё по лоту на одной странице</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Параметр</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Номер закупки</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>B1510261835045 (коммерческий тендер, Росэлторг — коммерческие закупки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ссылка</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.roseltorg.ru/procedures/search?query_field=B1510261835045</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Заказчик</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>АНО «Таврида.Арт», ИНН 9709042014; kontrakt@tavrida.art, +7 (495) 668-80-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>до 30.10.2026 12:00 МСК</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Место поставки</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>РФ, Республика Крым, г. Судак, арт-кластер «Таврида»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Срок поставки</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>10 календарных дней с даты заключения договора — нужен товар в наличии</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Оплата</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>30 календарных дней после подписания УПД и акта приёмки; аванса нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Гарантия</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>не менее 12 месяцев</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Состав</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>8 позиций: 145 комплектов (костюм, кофта, куртка, шапка, полуботинки, жилет) + 170 перчаток + 170 снудов; размеры 50–54, обувь 42–45; цвет чёрный</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>НМЦК</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4169750</v>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Себестоимость с доставкой</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2925900</v>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Маржа при НМЦК</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0.2983032555908628</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Безубыточное снижение</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>0.2693888846601725</v>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Наша цена заявки (−10%)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3752710</v>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Прибыль после УСН при этой цене</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>595505.1952876712</v>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Риски</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>цены кофты, полуботинок, жилета, перчаток — розница/поиск, нужны КП; производство подтверждено только у Сплава и Урсуса; доставка в Крым — оценка 120 тыс., нужен расчёт ТК; проверки Росмолодёжи (субсидия)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Что сделать</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>1) запросить КП у Урсуса и Сплава (лист «Поставщики (КП)»); 2) расчёт доставки в Судак у ТК; 3) заполнить Прил. 2 ценами с листа «Цены для заявки»; 4) подать до 30.10 12:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -506,7 +748,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>АНО «Таврида.Арт» B1510261835045 — форменная одежда службы безопасности (Судак). Подача 30.10.2026 12:00 МСК, Росэлторг (коммерческий тендер)</t>
         </is>
@@ -536,385 +778,385 @@
       <c r="I2" s="2" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Себес за ед., ₽</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Сумма себеса, ₽</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Вес ед., кг</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Основной источник цены</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Подтверждение</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Тактический костюм (демисезонный)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="5" t="n">
         <v>3350</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="5" t="n">
         <v>485750</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Урсус (ursus.ru), производитель/опт: 2875 ₽ — Костюм СПЕЦНАЗ КОС501, рип-стоп 65/35 220 г/м2 ВО, чёрный, накладки локоть/колено; опт 2875, кр.опт 2645</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>B (живой складской остаток на 20.10.2026</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>https://www.ursus.ru/catalogue/product/kostyum_spetsnaz_2021/</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Тактическая кофта (флисовая)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="5" t="n">
         <v>2300</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="5" t="n">
         <v>333500</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Урсус: 1500 ₽ — Толстовка флисовая H23010 чёрная, опт 1500, розн 2325; без водоотталкивающих вставок</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>B (живая карточка; остаток 48-54 = 0 — п</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>https://www.ursus.ru/catalogue/product/kurtka_flisovaya_h23010_tsvet_chernyy/</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Тактическая куртка с капюшоном (зимняя)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="5" t="n">
         <v>3500</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="5" t="n">
         <v>507500</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Урсус — Куртка Охрана зимняя чёрная (есть с капюшоном): 2650 ₽ — оксфорд 100% ПЭ — не 35/65 и без фольги; кр.опт 2438, розн 4108; версия с капюшоном 1</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>B (живой остаток 2152 шт; 52-54 — 284 шт</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>https://www.ursus.ru/catalogue/product/kurtka_muzhskaya_okhrana_zimnyaya_chernaya/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Тактическая шапка (зимняя)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="5" t="n">
         <v>550</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="5" t="n">
         <v>79750</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Урсус — шапка трикотажная чёрная двойная вязка: 151 ₽ — 100% ПАН — нижняя граница, не шерсть</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>B (живой остаток 2209 шт)</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>https://www.ursus.ru/catalogue/product/shapka_trikotazhnaya_chernaya_dvoynaya_vyazka_6_klass/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Полуботинки (утепленные)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="5" t="n">
         <v>2900</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="5" t="n">
         <v>420500</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Сплав — полуботинки тактические 10717: 3660 ₽ — зимние тактические ботинки Сплав 4440–10070</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>B (©2026, раздел каталога; цена из поиск</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>https://www.splav.ru/catalog/military-tactics/novyj-obuv/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Жилет разгрузочный тактический</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="5" t="n">
         <v>4500</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="5" t="n">
         <v>652500</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>АРМИШОП (armishop.ru) — Plate Carrier Molle Black: 5610 ₽ — нейлон 500D, без бронеплит</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>C (поисковая выдача: в наличии 99 шт; са</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>https://armishop.ru/shop/razgruzochnyy-zhilet-plate-carriere-molle-black</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Тактические перчатки (зимние)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="9" t="n">
         <v>170</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="5" t="n">
         <v>255000</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Garsing — перчатки ТУЧИ чёрные GSG-54: 2890 ₽ — там же «Тактические чёрные 7.62» 1075 ₽, «324 пластиковая защита» 500 ₽</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>B (живой каталог, «в наличии на складе»)</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>https://garsingshop.ru/catalog/odezhda_ash/perchatki_/takticheskie_/</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Тактический снуд</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="9" t="n">
         <v>170</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="5" t="n">
         <v>420</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="5" t="n">
         <v>71400</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Урсус — бафф Nesse чёрный: 415 ₽ — полиэстер 100% флис 300 г/м2; кр.опт 382, розн 480</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>B (остаток 1905 шт)</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>https://www.ursus.ru/catalogue/product/baff_nesse_chernyy/</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Доставка Москва → Судак (~0,95 т), оценка</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="6" t="n">
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
         <v>120000</v>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>ОЦЕНКА, не котировка: ~145 мест, ~0.95 т (6.5 кг/комплект), ~7–8 м3. Сборный груз ДЛ/ПЭК/КИТ Москва→Симферополь + довоз до Судака ~70–100 тыс ₽; отдел</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="7" t="inlineStr"/>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr"/>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>ИТОГО себестоимость</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="8" t="n">
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="11" t="n">
         <v>2925900</v>
       </c>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -932,7 +1174,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -948,176 +1190,176 @@
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="C1" s="11" t="n"/>
-      <c r="D1" s="11" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>НМЦК, ₽</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="5" t="n">
         <v>4169750</v>
       </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Себестоимость, ₽</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="5" t="n">
         <v>2925900</v>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Маржа при НМЦК</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="6" t="n">
         <v>0.2983032555908628</v>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Безубыточное снижение</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="6" t="n">
         <v>0.2693888846601725</v>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Снижение</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Цена заявки, ₽</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>Прибыль после УСН, ₽</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Маржа к цене</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="5" t="n">
         <v>4169750</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="5" t="n">
         <v>947153.3232876712</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="6" t="n">
         <v>0.2271487075454575</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="5" t="n">
         <v>3961262.5</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="5" t="n">
         <v>771356.6632876713</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="6" t="n">
         <v>0.1947249553110079</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="5" t="n">
         <v>3752775</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="5" t="n">
         <v>595560.0032876713</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.1586985639393972</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="5" t="n">
         <v>3544287.5</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="5" t="n">
         <v>419763.3432876712</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="6" t="n">
         <v>0.1184337735828911</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="5" t="n">
         <v>3335800</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="5" t="n">
         <v>243966.6832876712</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="6" t="n">
         <v>0.07313588443182183</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="5" t="n">
         <v>3127312.5</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="5" t="n">
         <v>68170.02328767124</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="6" t="n">
         <v>0.02179827672727661</v>
       </c>
     </row>
@@ -1127,7 +1369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1145,7 +1387,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Спецификация (Прил. 2) — наше предложение, ≈ −10% от НМЦК; доставка включена в цены</t>
         </is>
@@ -1157,254 +1399,254 @@
       <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Перечень товаров</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Цена за ед., руб.</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Сумма, руб.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Тактический костюм (демисезонный)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="5" t="n">
         <v>4479</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="5" t="n">
         <v>649455</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Тактическая кофта (флисовая)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="5" t="n">
         <v>3076</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="5" t="n">
         <v>446020</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Тактическая куртка с капюшоном (зимняя)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="5" t="n">
         <v>4681</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="5" t="n">
         <v>678745</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Тактическая шапка (зимняя)</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="5" t="n">
         <v>736</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="5" t="n">
         <v>106720</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Полуботинки (утепленные)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="5" t="n">
         <v>3879</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="5" t="n">
         <v>562455</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Жилет разгрузочный тактический</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="5" t="n">
         <v>6019</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>872755</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Тактические перчатки (зимние)</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="9" t="n">
         <v>170</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="5" t="n">
         <v>2006</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="n">
         <v>341020</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Тактический снуд</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="9" t="n">
         <v>170</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="5" t="n">
         <v>562</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="5" t="n">
         <v>95540</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="7" t="inlineStr"/>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr"/>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>ИТОГО (НДС не облагается, УСН)</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8" t="n">
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="11" t="n">
         <v>3752710</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Снижение от НМЦК: 10.0%; прибыль после УСН ≈ 595 505 ₽</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1412,27 +1654,30 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Кому отправить запрос КП по «Таврида.Арт» — нужна цена и наличие на 145 комплектов (р. 50–54, обувь 42–45), поставка в Судак за 10 дней</t>
         </is>
@@ -1444,208 +1689,238 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
     </row>
     <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Какие позиции запросить</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Звонок: результат</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Цены КП</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Наличие / срок</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Урсус</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>производитель — подтверждено на сайте: «собственное производство одежды и обуви с 1998 г.»</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>1 костюм (+наколенники/налокотники Блок-Х), 2 флисовая кофта, 3 зимняя куртка «Охрана», 4 шапка, 7 перчатки, 8 снуд</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>8 (495) 564-88-88</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>zakaz@ursu.ru</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>https://www.ursus.ru</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>костюм, куртка, снуд — в наличии по оптовым ценам; основной поставщик</t>
         </is>
       </c>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Сплав</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>производитель — подтверждено: 3 фабрики (Москва, Тверь, Новозыбков)</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>1 костюм, 2 флисовая кофта (Кречет Pro), 3 зимняя куртка, 5 полуботинки 10717, 6 жилет разгрузочный</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>+7 495 984-28-83 (опт)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>opt@splav.ru</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>https://www.splav.ru</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>оптовый отдел; цены на сайте — розница, просить опт</t>
         </is>
       </c>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Garsing</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>бренд обуви/снаряжения — собственное производство НЕ подтверждено</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>5 полуботинки утеплённые («Путешественник флис»), 7 перчатки зимние тактические (ТУЧИ)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>+7 (498) 602-69-01</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>marketing@garsing.ru</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>https://garsing.ru</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>уточнить чёрный цвет и наличие размеров 42–45</t>
         </is>
       </c>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>ГК «Спецобъединение»</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>оптовик/поставщик СИЗ — производство НЕ подтверждено</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>3 зимняя куртка, 5 полуботинки утеплённые, 7 перчатки — запасной вариант</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>+7 (495) 011-44-00</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>mail@spets.ru</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>https://www.spets.ru</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>прайс 2026 на сайте (price_msk.xls)</t>
         </is>
       </c>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/TAVRIDA_B1510261835045.xlsx
+++ b/TAVRIDA_B1510261835045.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Маржа" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены для заявки" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Поставщики (КП)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Построчная проверка" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -48,7 +49,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +59,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -133,6 +144,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -651,7 +668,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2925900</v>
+        <v>3440900</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
@@ -661,7 +678,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.2983032555908628</v>
+        <v>0.1747946519575514</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
@@ -671,17 +688,17 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.2693888846601725</v>
+        <v>0.1407909406429432</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Наша цена заявки (−10%)</t>
+          <t>Наша цена заявки (−5%)</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3752710</v>
+        <v>3961190</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
@@ -691,7 +708,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>595505.1952876712</v>
+        <v>319153.7504657534</v>
       </c>
     </row>
     <row r="18" ht="50" customHeight="1">
@@ -702,7 +719,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>цены кофты, полуботинок, жилета, перчаток — розница/поиск, нужны КП; производство подтверждено только у Сплава и Урсуса; доставка в Крым — оценка 120 тыс., нужен расчёт ТК; проверки Росмолодёжи (субсидия)</t>
+          <t>после построчной проверки себес вырос на ~0,5 млн; зимняя куртка по ТЗ (35/65, фольга, несъёмный капюшон) нигде не найдена — нужен пошив/КП; наличие на 10 дней подтверждено только у костюма и снуда (Урсус); полуботинки по формулировке ТЗ — вероятно импорт (Outventure); производство подтверждено только у Сплава и Урсуса; доставка в Крым — оценка 120 тыс., нужен расчёт ТК; проверки Росмолодёжи (субсидия)</t>
         </is>
       </c>
     </row>
@@ -874,10 +891,10 @@
         <v>145</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>333500</v>
+        <v>478500</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.6</v>
@@ -911,10 +928,10 @@
         <v>145</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>507500</v>
+        <v>652500</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>1.6</v>
@@ -948,10 +965,10 @@
         <v>145</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>79750</v>
+        <v>94250</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.12</v>
@@ -985,10 +1002,10 @@
         <v>145</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2900</v>
+        <v>3500</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>420500</v>
+        <v>507500</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.2</v>
@@ -1022,10 +1039,10 @@
         <v>145</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>652500</v>
+        <v>725000</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1.3</v>
@@ -1059,10 +1076,10 @@
         <v>170</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>255000</v>
+        <v>306000</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.2</v>
@@ -1151,7 +1168,7 @@
       <c r="C13" s="10" t="inlineStr"/>
       <c r="D13" s="10" t="inlineStr"/>
       <c r="E13" s="11" t="n">
-        <v>2925900</v>
+        <v>3440900</v>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
@@ -1222,7 +1239,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2925900</v>
+        <v>3440900</v>
       </c>
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
@@ -1234,7 +1251,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>0.2983032555908628</v>
+        <v>0.1747946519575514</v>
       </c>
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
@@ -1246,7 +1263,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.2693888846601725</v>
+        <v>0.1407909406429432</v>
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
@@ -1287,10 +1304,10 @@
         <v>4169750</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>947153.3232876712</v>
+        <v>495011.5424657534</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.2271487075454575</v>
+        <v>0.1187149211501297</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
@@ -1301,10 +1318,10 @@
         <v>3961262.5</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>771356.6632876713</v>
+        <v>319214.8824657535</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.1947249553110079</v>
+        <v>0.08058412752645236</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
@@ -1315,10 +1332,10 @@
         <v>3752775</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>595560.0032876713</v>
+        <v>143418.2224657534</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.1586985639393972</v>
+        <v>0.0382165790556997</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
@@ -1329,10 +1346,10 @@
         <v>3544287.5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>419763.3432876712</v>
+        <v>-38092.27945205479</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.1184337735828911</v>
+        <v>-0.0107475139790592</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
@@ -1343,10 +1360,10 @@
         <v>3335800</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>243966.6832876712</v>
+        <v>-244911.8794520548</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.07313588443182183</v>
+        <v>-0.07341923360275041</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
@@ -1357,10 +1374,10 @@
         <v>3127312.5</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>68170.02328767124</v>
+        <v>-451731.4794520548</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.02179827672727661</v>
+        <v>-0.1444471825096004</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1406,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>Спецификация (Прил. 2) — наше предложение, ≈ −10% от НМЦК; доставка включена в цены</t>
+          <t>Спецификация (Прил. 2) — наше предложение, ≈ −5% от НМЦК (после построчной проверки цен); доставка включена в цены</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1448,10 +1465,10 @@
         <v>145</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4479</v>
+        <v>3996</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>649455</v>
+        <v>579420</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
@@ -1472,10 +1489,10 @@
         <v>145</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3076</v>
+        <v>3936</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>446020</v>
+        <v>570720</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
@@ -1496,10 +1513,10 @@
         <v>145</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4681</v>
+        <v>5368</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>678745</v>
+        <v>778360</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
@@ -1520,10 +1537,10 @@
         <v>145</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>736</v>
+        <v>775</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>106720</v>
+        <v>112375</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
@@ -1544,10 +1561,10 @@
         <v>145</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3879</v>
+        <v>4175</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>562455</v>
+        <v>605375</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
@@ -1568,10 +1585,10 @@
         <v>145</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>6019</v>
+        <v>5964</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>872755</v>
+        <v>864780</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
@@ -1592,10 +1609,10 @@
         <v>170</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2006</v>
+        <v>2147</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>341020</v>
+        <v>364990</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
@@ -1616,10 +1633,10 @@
         <v>170</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>562</v>
+        <v>501</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>95540</v>
+        <v>85170</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
@@ -1633,14 +1650,14 @@
       <c r="D11" s="10" t="inlineStr"/>
       <c r="E11" s="10" t="inlineStr"/>
       <c r="F11" s="11" t="n">
-        <v>3752710</v>
+        <v>3961190</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="4" t="inlineStr"/>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Снижение от НМЦК: 10.0%; прибыль после УСН ≈ 595 505 ₽</t>
+          <t>Снижение от НМЦК: 5.0%; прибыль после УСН ≈ 319 154 ₽</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -1932,4 +1949,633 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Построчная проверка 20.10.2026: каждая позиция сверена с ТЗ и с 3+ источниками 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Было, ₽/ед.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Медиана источников</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Итоговая цена, ₽/ед.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Изменение суммы, ₽</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Вердикт</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Надёжность</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Соответствие ТЗ</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Производитель подтверждён</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Нацрежим</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Источники (компания — цена)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="80" customHeight="1">
+      <c r="A3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Тактический костюм (демисезонный)</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>3350</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>3350</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">аналог: Урсус — куртка+брюки рип-стоп 65/35 с усилениями локоть/колено; ТЗ описывает кофту из 2 тканей (рукава/воротник </t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>частично: Урсус — поставщик-производитель спецодежды (ГОСТ/д</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>РФ (Урсус, пошив РФ по ГОСТ 12.4.280 — проверить с</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Урсус — Костюм СПЕЦНАЗ КОС501 чёрный, ри — 2875; Урсус — наколенники+налокотники съёмные  — 468; Garsing — Костюм Condor-2 CPS-16 чёрный  — 8660; Сплав — Костюм Полевой чёрный — 7000</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Медиана 7000 — по рознице (Сплав/Garsing), против оптовой цены Урсус 2875+468=3343 текущая 3350 корректна. Наличие 50/52/54 (44/62/39) покрывается остатком Урсус. Brand-name Condor/Сплав в 2–2.5 раза </t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Тактическая кофта (флисовая)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3990</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>145000</v>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>занижена</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>не совпадает: Урсус H23010/Twohand — гладкий флис без вставок из водонепроницаемого ПЭ, без патчкордов на плечах и без в</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>нет для подходящей модели (Урсус — не по ТЗ; Garsing — произ</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">не проверено (ГоркаФрол/Garsing — уточнить страну </t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Урсус — Толстовка флисовая H23010 чёрная — 1500; Урсус — Куртка флисовая Twohand чёрная Г — 1747; ГоркаФрол — флисовая кофта тактическая ч — 3990; Garsing — Куртка SHERPA флис PF3-16 чёрн — 5690</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2300 на базе гладкой толстовки Урсус, которая ТЗ не соответствует и отсутствует в наличии в 48-54. Модель с вставками — розница 3990–5690; опт −15–25% → ~3300. Нужен КП швейного цеха (пошив 145 шт за </t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Тактическая куртка с капюшоном (зимняя)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>145000</v>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>занижена</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>не совпадает: Урсус — оксфорд 100% ПЭ, подклад ПЭ без фольги, капюшон СЪЁМНЫЙ, меховой воротник; Garsing Рекрут — таслан</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">нет (ни у одного подтверждённого производителя модели по ТЗ </t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>не проверено</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Урсус — Куртка «Охрана» зимняя чёрная КУ — 2650; Garsing — Куртка Рекрут TPTS-16 чёрная,  — 6500; Сплав — зимние куртки (Буран/Тюр Shelter — 11500; Форменный Патруль (patrul67.ru) — куртка — 4000</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Единственный «ТЗ-подобный» источник (patrul67, 4000) мёртв. Урсус 2650 дешевле, но по 3 параметрам (ткань, фольга, капюшон) не проходит. Рекомендация 4500 — оценка под пошив/маркетплейс-поставщика; кр</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Тактическая шапка (зимняя)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>597</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>14500</v>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>не совпадает по составу: подтверждённой модели шерсть 70%/акрил 30% + флисовая подкладка не найдено; Урсус ШАП702 — флис</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>не проверено (Marhatter — РФ бренд, пошив уточнить</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Урсус — Шапка на флисе трикотажная чёрна — 209; Урсус — Шапка Nordkapp чёрная (акрил 100 — 597; Сплав — Шапка п/ш Marhatter 13145-3 чёрн — 1050; Garsing — Шапка флис 350 SHERPA чёрная — 230</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Цена в коридоре ±15% от медианы, но товар по составу 70% шерсти не подтверждён; полушерстяные с флисом — 650–1050 розн. Рекомендую 650 и запрос КП трикотажной фабрики.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Полуботинки (утепленные)</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3595</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>87000</v>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>занижена</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>аналог: ТЗ списано с карточки Outventure (+ADD DRY — фирменная пропитка Спортмастера); у Сплав/Garsing соответствие по ф</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>частично: Garsing — производитель обуви (garsing.ru), зимняя</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>импорт — Outventure (Китай); замена: Garsing/Сплав</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Сплав — полуботинки тактические 10717 — 3660; Garsing — полуботинки «Путешественник» 0 — 3530; Outventure (Спортмастер) — первоисточник — 4000</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>Размерный ряд 42–45, из них 43 — 92 пары: наличие критично. 2900 на 19% ниже медианы розницы; с оптовой скидкой реалистично 3200–3500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Жилет разгрузочный тактический</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5610</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>72500</v>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>занижена</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>аналог: Armishop/CIRAS — плитоноски MOLLE с карманами под плиты, но материал нейлон 500D/оксфорд, а не кордура + вспенен</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>нет (Ифрит через Урсус — цена не получена; сайты Стич Профи/</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>импорт — вероятно Китай; замена: Ифрит (Урсус), Ст</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>АРМИШОП — Plate Carrier Molle Black, ней — 5610; Полигон — CIRAS Molle чёрный, карманы SA — 7999; Pnevmat24 — жилет MOLLE Black VT021B (по — 1890; Урсус — Жилет разгрузочный Ифрит «Basili — 0</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>4500 на 20% ниже медианы; в рознице подходящая модель 5610–7999. 145 шт в наличии — только Armishop (99 шт по выдаче). Рекомендация 5000 при оптовой скидке; запросить КП Ифрит/Урсус.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Тактические перчатки (зимние)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2188</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>51000</v>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>занижена</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>аналог: только КМФ78 совпадает (зимние + защита костяшек), но нет в наличии; Garsing ТУЧИ/Хитин — защита есть, утепление</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>частично: Garsing — производитель (garsing.ru), модели GSG —</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>не проверено (вероятно импорт — Китай)</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Garsing — Перчатки «ТУЧИ» чёрные GSG-54 — 2890; Garsing — Перчатки GSG-75 чёрные (раздел — 825; Garsing — Перчатки Nordkapp Veho 2WN Bla — 1485; КМФ78 — утеплённые с защитой костяшек, ф — 3013</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>1500 на 31% ниже медианы; с учётом опта рекомендую 1800. 170 пар в наличии ни у одного источника не подтверждено.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Тактический снуд</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>415</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>аналог: Nesse — полиэстер 100% (соответствует составу), но флис 300 г/м2 — тёплый, ТЗ «демисезон, защита от солнца/ветра</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>частично: Урсус — поставщик-производитель спецодежды (ГОСТ/д</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>не проверено</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Урсус — Бафф Nesse чёрный ГФ15736.30, по — 415; Урсус — Бафф Хлопок-2 чёрный (хлопок/лай — 400; Сплав — мультибандана (Rain/Fresh и др.) — 760</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Цена подтверждена, наличие 1905 шт перекрывает 170.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="10" t="inlineStr"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>ИТОГО товары</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="11" t="n">
+        <v>2805900</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr"/>
+      <c r="F11" s="11" t="n">
+        <v>3320900</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>515000</v>
+      </c>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="12" t="n"/>
+      <c r="N11" s="12" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>